--- a/labs/lab-5/downloads/Lab_5_Consultant_and_BA_Prompt_Library.xlsx
+++ b/labs/lab-5/downloads/Lab_5_Consultant_and_BA_Prompt_Library.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Catalogue" sheetId="1" r:id="Rce89149791ad4f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Text" sheetId="2" r:id="Raeeac3ced19b4eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="3" r:id="R84e67896aae94869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Requests" sheetId="4" r:id="Rd3fc7119fc424b57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version History" sheetId="5" r:id="Ra898d12aef51491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired Prompts" sheetId="6" r:id="R49f48d30852c40c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="7" r:id="R3d9db01b4cad4685"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R5fed77a1de604449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Catalogue" sheetId="1" r:id="Re197ceb910d447ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Text" sheetId="2" r:id="Rdb6c8253ace34c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="3" r:id="R4ba167a1d6c24dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Requests" sheetId="4" r:id="R0ef016a71a354939"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version History" sheetId="5" r:id="Rdc1d3152b6b44102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired Prompts" sheetId="6" r:id="R7a644dcf224d42e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="7" r:id="Rf854d89a1f674252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R405c070ca73a478e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2225,7 +2225,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="28" t="str">
-        <x:v>Retain complete prior prompt text or its controlled reference for rollback.</x:v>
+        <x:v>Use Copilot in Excel Edit mode to write approved versions; retain the prior prompt or controlled reference for rollback.</x:v>
       </x:c>
       <x:c r="B2" s="27"/>
       <x:c r="C2" s="27"/>
@@ -2315,7 +2315,7 @@
         <x:v>Two-case approved version</x:v>
       </x:c>
       <x:c r="G6" s="30" t="str">
-        <x:v>Paste approved complete prompt or controlled link</x:v>
+        <x:v>Copilot Edit mode: write approved prompt or controlled link</x:v>
       </x:c>
       <x:c r="H6" s="30" t="str"/>
       <x:c r="I6" s="30" t="str">
